--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Sources" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Comps'!$B$2:$J$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inclusion'!$B$2:$F$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Comps'!$B$2:$J$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inclusion'!$B$2:$F$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,6 +174,7 @@
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -557,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J58"/>
+  <dimension ref="B2:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -693,16 +694,16 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>1625000000</v>
+        <v>1636000000</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>4272000000</v>
+        <v>4853000000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>861300000</v>
+        <v>869700000</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>4212000000</v>
+        <v>4530000000</v>
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
@@ -761,16 +762,16 @@
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>1721000000</v>
+        <v>3222000000</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>1245000000</v>
+        <v>3152000000</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>3934300000</v>
+        <v>3970800000</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>50011000000</v>
+        <v>46585000000</v>
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
@@ -790,16 +791,16 @@
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>3933000000</v>
+        <v>5539000000</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>9348000000</v>
+        <v>16178000000</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>948300000</v>
+        <v>2638800000</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>8249000000</v>
+        <v>14265000000</v>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
@@ -819,7 +820,7 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>1345000000</v>
+        <v>5013000000</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -832,7 +833,7 @@
         </is>
       </c>
       <c r="H15" s="17" t="n">
-        <v>13813000000</v>
+        <v>23151000000</v>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
@@ -907,457 +908,457 @@
       <c r="H19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Fiscal year end</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Period covered</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
-        <v>10918000000</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>22680000000</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>35819000000</v>
-      </c>
-      <c r="G20" s="17" t="n">
-        <v>5507700000</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>54228000000</v>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="D22" s="17" t="n">
+        <v>26914000000</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>34639000000</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>63887000000</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>8194600000</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>52853000000</v>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>[15][16][17][18][19]</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>10460000000</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>24690000000</v>
-      </c>
-      <c r="G21" s="17" t="n">
-        <v>2293600000</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>21711000000</v>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>[20][21][22][23]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    % gross margin</t>
-        </is>
-      </c>
-      <c r="D22" s="19">
-        <f>IFERROR(D21/D20,"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="19">
-        <f>IFERROR(E21/E20,"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="19">
-        <f>IFERROR(F21/F20,"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="19">
-        <f>IFERROR(G21/G20,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="19">
-        <f>IFERROR(H21/H20,"")</f>
-        <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="9" t="inlineStr">
         <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>17152000000</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>43294000000</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>4180700000</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>18375000000</v>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>[20][21][22][23]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    % gross margin</t>
+        </is>
+      </c>
+      <c r="D24" s="20">
+        <f>IFERROR(D23/D22,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="20">
+        <f>IFERROR(E23/E22,"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="20">
+        <f>IFERROR(F23/F22,"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="20">
+        <f>IFERROR(G23/G22,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="20">
+        <f>IFERROR(H23/H22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
           <t>Operating income</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>401000000</v>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>16207000000</v>
-      </c>
-      <c r="G23" s="17" t="n">
-        <v>-567700000</v>
-      </c>
-      <c r="H23" s="17" t="n">
-        <v>93000000</v>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>3694000000</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>25484000000</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>1322900000</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>-2214000000</v>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>[24][25][26][27]</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="9" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="14" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="D25" s="15">
-        <f>IFERROR(D23+D24,"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="15">
-        <f>IFERROR(E23+E24,"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="15">
-        <f>IFERROR(F23+F24,"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="15">
-        <f>IFERROR(G23+G24,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="15">
-        <f>IFERROR(H23+H24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="18" t="inlineStr">
+      <c r="D27" s="15">
+        <f>IFERROR(D25+D26,"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="15">
+        <f>IFERROR(E25+E26,"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="15">
+        <f>IFERROR(F25+F26,"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="15">
+        <f>IFERROR(G25+G26,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="15">
+        <f>IFERROR(H25+H26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">    % EBITDA margin</t>
         </is>
       </c>
-      <c r="D26" s="19">
-        <f>IFERROR(D25/D20,"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="19">
-        <f>IFERROR(E25/E20,"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="19">
-        <f>IFERROR(F25/F20,"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="19">
-        <f>IFERROR(G25/G20,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="19">
-        <f>IFERROR(H25/H20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="D28" s="20">
+        <f>IFERROR(D27/D22,"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="20">
+        <f>IFERROR(E27/E22,"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="20">
+        <f>IFERROR(F27/F22,"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="20">
+        <f>IFERROR(G27/G22,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="20">
+        <f>IFERROR(H27/H22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>854000000</v>
-      </c>
-      <c r="F27" s="17" t="n">
-        <v>11495000000</v>
-      </c>
-      <c r="G27" s="17" t="n">
-        <v>-933400000</v>
-      </c>
-      <c r="H27" s="17" t="n">
-        <v>1689000000</v>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>4335000000</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>5895000000</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>2670100000</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>-267000000</v>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>[28][29][30][31]</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F28" s="21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G28" s="21" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="H28" s="21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>[32][33][34][35]</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="7" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Trailing multiples</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>EV / Revenue</t>
-        </is>
-      </c>
-      <c r="D31" s="22">
-        <f>IFERROR(D17/D20,"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="22">
-        <f>IFERROR(E17/E20,"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="22">
-        <f>IFERROR(F17/F20,"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="22">
-        <f>IFERROR(G17/G20,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="22">
-        <f>IFERROR(H17/H20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="D32" s="22">
-        <f>IFERROR(D17/D25,"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="22">
-        <f>IFERROR(E17/E25,"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="22">
-        <f>IFERROR(F17/F25,"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="22">
-        <f>IFERROR(G17/G25,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="22">
-        <f>IFERROR(H17/H25,"")</f>
-        <v/>
-      </c>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="9" t="inlineStr">
         <is>
+          <t>EV / Revenue</t>
+        </is>
+      </c>
+      <c r="D33" s="23">
+        <f>IFERROR(D17/D22,"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="23">
+        <f>IFERROR(E17/E22,"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="23">
+        <f>IFERROR(F17/F22,"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="23">
+        <f>IFERROR(G17/G22,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="23">
+        <f>IFERROR(H17/H22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="D34" s="23">
+        <f>IFERROR(D17/D27,"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="23">
+        <f>IFERROR(E17/E27,"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="23">
+        <f>IFERROR(F17/F27,"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="23">
+        <f>IFERROR(G17/G27,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="23">
+        <f>IFERROR(H17/H27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
           <t>P / E</t>
         </is>
       </c>
-      <c r="D33" s="22">
-        <f>IFERROR(D8/D28,"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="22">
-        <f>IFERROR(E8/E28,"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="22">
-        <f>IFERROR(F8/F28,"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="22">
-        <f>IFERROR(G8/G28,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="22">
-        <f>IFERROR(H8/H28,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="7" t="inlineStr">
+      <c r="D35" s="23">
+        <f>IFERROR(D8/D30,"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="23">
+        <f>IFERROR(E8/E30,"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="23">
+        <f>IFERROR(F8/F30,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="23">
+        <f>IFERROR(G8/G30,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="23">
+        <f>IFERROR(H8/H30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Forward consensus (your input — not from filings)</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>NTM revenue (input)</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>NTM EBITDA (input)</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>NTM EPS (input)</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
+          <t>NTM revenue (input)</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1366,184 +1367,186 @@
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>EV / NTM revenue</t>
-        </is>
-      </c>
-      <c r="D39" s="22">
-        <f>IFERROR(D17/D36,"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="22">
-        <f>IFERROR(E17/E36,"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="22">
-        <f>IFERROR(F17/F36,"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="22">
-        <f>IFERROR(G17/G36,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="22">
-        <f>IFERROR(H17/H36,"")</f>
-        <v/>
+          <t>NTM EBITDA (input)</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>EV / NTM EBITDA</t>
-        </is>
-      </c>
-      <c r="D40" s="22">
-        <f>IFERROR(D17/D37,"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="22">
-        <f>IFERROR(E17/E37,"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="22">
-        <f>IFERROR(F17/F37,"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="22">
-        <f>IFERROR(G17/G37,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="22">
-        <f>IFERROR(H17/H37,"")</f>
-        <v/>
+          <t>NTM EPS (input)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="9" t="inlineStr">
         <is>
+          <t>EV / NTM revenue</t>
+        </is>
+      </c>
+      <c r="D41" s="23">
+        <f>IFERROR(D17/D38,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="23">
+        <f>IFERROR(E17/E38,"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="23">
+        <f>IFERROR(F17/F38,"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="23">
+        <f>IFERROR(G17/G38,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="23">
+        <f>IFERROR(H17/H38,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>EV / NTM EBITDA</t>
+        </is>
+      </c>
+      <c r="D42" s="23">
+        <f>IFERROR(D17/D39,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="23">
+        <f>IFERROR(E17/E39,"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="23">
+        <f>IFERROR(F17/F39,"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="23">
+        <f>IFERROR(G17/G39,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="23">
+        <f>IFERROR(H17/H39,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="9" t="inlineStr">
+        <is>
           <t>Forward P / E</t>
         </is>
       </c>
-      <c r="D41" s="22">
-        <f>IFERROR(D8/D38,"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="22">
-        <f>IFERROR(E8/E38,"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="22">
-        <f>IFERROR(F8/F38,"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="22">
-        <f>IFERROR(G8/G38,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="22">
-        <f>IFERROR(H8/H38,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="7" t="inlineStr">
+      <c r="D43" s="23">
+        <f>IFERROR(D8/D40,"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="23">
+        <f>IFERROR(E8/E40,"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="23">
+        <f>IFERROR(F8/F40,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="23">
+        <f>IFERROR(G8/G40,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="23">
+        <f>IFERROR(H8/H40,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Set statistics</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>Trailing EV / Revenue — median</t>
-        </is>
-      </c>
-      <c r="D44" s="24">
-        <f>IFERROR(MEDIAN(D31:H31),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>Trailing EV / Revenue — mean</t>
-        </is>
-      </c>
-      <c r="D45" s="24">
-        <f>IFERROR(AVERAGE(D31:H31),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Trailing EV / EBITDA — median</t>
-        </is>
-      </c>
-      <c r="D46" s="24">
-        <f>IFERROR(MEDIAN(D32:H32),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="25" t="inlineStr">
+          <t>Trailing EV / Revenue — median</t>
+        </is>
+      </c>
+      <c r="D46" s="25">
+        <f>IFERROR(MEDIAN(D33:H33),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1552,29 +1555,29 @@
     <row r="47">
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>Trailing EV / EBITDA — mean</t>
-        </is>
-      </c>
-      <c r="D47" s="24">
-        <f>IFERROR(AVERAGE(D32:H32),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="25" t="inlineStr">
+          <t>Trailing EV / Revenue — mean</t>
+        </is>
+      </c>
+      <c r="D47" s="25">
+        <f>IFERROR(AVERAGE(D33:H33),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1583,29 +1586,29 @@
     <row r="48">
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>Trailing P / E — median</t>
-        </is>
-      </c>
-      <c r="D48" s="24">
-        <f>IFERROR(MEDIAN(D33:H33),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F48" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="25" t="inlineStr">
+          <t>Trailing EV / EBITDA — median</t>
+        </is>
+      </c>
+      <c r="D48" s="25">
+        <f>IFERROR(MEDIAN(D34:H34),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1614,29 +1617,29 @@
     <row r="49">
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>Trailing P / E — mean</t>
-        </is>
-      </c>
-      <c r="D49" s="24">
-        <f>IFERROR(AVERAGE(D33:H33),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="25" t="inlineStr">
+          <t>Trailing EV / EBITDA — mean</t>
+        </is>
+      </c>
+      <c r="D49" s="25">
+        <f>IFERROR(AVERAGE(D34:H34),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1645,29 +1648,29 @@
     <row r="50">
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>Forward EV / Revenue — median</t>
-        </is>
-      </c>
-      <c r="D50" s="24">
-        <f>IFERROR(MEDIAN(D39:H39),"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="25" t="inlineStr">
+          <t>Trailing P / E — median</t>
+        </is>
+      </c>
+      <c r="D50" s="25">
+        <f>IFERROR(MEDIAN(D35:H35),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1676,29 +1679,29 @@
     <row r="51">
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>Forward EV / Revenue — mean</t>
-        </is>
-      </c>
-      <c r="D51" s="24">
-        <f>IFERROR(AVERAGE(D39:H39),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="25" t="inlineStr">
+          <t>Trailing P / E — mean</t>
+        </is>
+      </c>
+      <c r="D51" s="25">
+        <f>IFERROR(AVERAGE(D35:H35),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1707,29 +1710,29 @@
     <row r="52">
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>Forward EV / EBITDA — median</t>
-        </is>
-      </c>
-      <c r="D52" s="24">
-        <f>IFERROR(MEDIAN(D40:H40),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="25" t="inlineStr">
+          <t>Forward EV / Revenue — median</t>
+        </is>
+      </c>
+      <c r="D52" s="25">
+        <f>IFERROR(MEDIAN(D41:H41),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1738,29 +1741,29 @@
     <row r="53">
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>Forward EV / EBITDA — mean</t>
-        </is>
-      </c>
-      <c r="D53" s="24">
-        <f>IFERROR(AVERAGE(D40:H40),"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="25" t="inlineStr">
+          <t>Forward EV / Revenue — mean</t>
+        </is>
+      </c>
+      <c r="D53" s="25">
+        <f>IFERROR(AVERAGE(D41:H41),"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1769,29 +1772,29 @@
     <row r="54">
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>Forward P / E — median</t>
-        </is>
-      </c>
-      <c r="D54" s="24">
-        <f>IFERROR(MEDIAN(D41:H41),"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="25" t="inlineStr">
+          <t>Forward EV / EBITDA — median</t>
+        </is>
+      </c>
+      <c r="D54" s="25">
+        <f>IFERROR(MEDIAN(D42:H42),"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1800,45 +1803,114 @@
     <row r="55">
       <c r="B55" s="18" t="inlineStr">
         <is>
+          <t>Forward EV / EBITDA — mean</t>
+        </is>
+      </c>
+      <c r="D55" s="25">
+        <f>IFERROR(AVERAGE(D42:H42),"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>Forward P / E — median</t>
+        </is>
+      </c>
+      <c r="D56" s="25">
+        <f>IFERROR(MEDIAN(D43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="18" t="inlineStr">
+        <is>
           <t>Forward P / E — mean</t>
         </is>
       </c>
-      <c r="D55" s="24">
-        <f>IFERROR(AVERAGE(D41:H41),"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="26" t="inlineStr">
+      <c r="D57" s="25">
+        <f>IFERROR(AVERAGE(D43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="E57" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>Shaded blue cells are yours to fill: price and consensus are not filing data, so this workbook will not guess them.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="26" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>Multiples recompute from the cells above. Never hard-code a multiple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>CALENDARISATION REQUIRED: these filers do not share a fiscal year end (Dec, Jan, Nov). The multiples above compare different twelve-month windows. Calendarise to a common year end before using them, and say in the footnote which filers were adjusted and how.</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D30"/>
+  <dimension ref="B2:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1886,7 +1958,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Fill the rationale column before you show this to anyone. Business-model similarity, size band, growth band, margin structure and end-market exposure are the five tests that survive scrutiny.</t>
         </is>
@@ -1898,7 +1970,7 @@
           <t>NVDA — NVIDIA CORP</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -1910,7 +1982,7 @@
           <t>AMD — ADVANCED MICRO DEVICES INC</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -1922,7 +1994,7 @@
           <t>AVGO — Broadcom Inc.</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -1934,7 +2006,7 @@
           <t>MRVL — Marvell Technology, Inc.</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -1946,7 +2018,7 @@
           <t>INTC — INTEL CORP</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -1960,7 +2032,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>An empty rejection list is a red flag. If you did not reject anyone, you did not build a set, you took a sector list.</t>
         </is>
@@ -1972,7 +2044,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -1984,7 +2056,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -1996,7 +2068,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2008,7 +2080,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2020,7 +2092,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2032,7 +2104,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2041,60 +2113,134 @@
     <row r="25">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Adjustments made</t>
+          <t>Calendarisation</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>Note every adjustment here: stock-based compensation treatment, operating leases capitalised or not, non-recurring items excluded, fiscal-year calendarisation. An unstated adjustment is the fastest way to lose the room.</t>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>Fiscal year ends Jan · latest period FY2022</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>[adjustment]</t>
-        </is>
-      </c>
-      <c r="D27" s="27" t="inlineStr">
-        <is>
-          <t>[what and why]</t>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>Fiscal year ends Dec · latest period FY2025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>[adjustment]</t>
-        </is>
-      </c>
-      <c r="D28" s="27" t="inlineStr">
-        <is>
-          <t>[what and why]</t>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>Fiscal year ends Nov · latest period FY2025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>[adjustment]</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>[what and why]</t>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>Fiscal year ends Jan · latest period FY2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="9" t="inlineStr">
         <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="D30" s="28" t="inlineStr">
+        <is>
+          <t>Fiscal year ends Dec · latest period FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Year ends differ across the set. State the common year end you calendarised to and which filers were stubbed, or the comparison is not a comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Adjustments made</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Note every adjustment here: stock-based compensation treatment, operating leases capitalised or not, non-recurring items excluded, fiscal-year calendarisation. An unstated adjustment is the fastest way to lose the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
           <t>[adjustment]</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D35" s="28" t="inlineStr">
+        <is>
+          <t>[what and why]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>[adjustment]</t>
+        </is>
+      </c>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>[what and why]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>[adjustment]</t>
+        </is>
+      </c>
+      <c r="D37" s="28" t="inlineStr">
+        <is>
+          <t>[what and why]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>[adjustment]</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="inlineStr">
         <is>
           <t>[what and why]</t>
         </is>
@@ -2145,7 +2291,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Share price and forward consensus are user inputs and carry no filing provenance by design.</t>
         </is>
@@ -2179,7 +2325,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="30" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -2187,24 +2333,24 @@
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2023-12-30 · shares · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-12-27 · shares · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="30" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -2212,24 +2358,24 @@
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2023-10-29 · shares · filed 2025-12-18</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-11-02 · shares · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="30" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -2237,24 +2383,24 @@
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2024-02-03 · shares · filed 2026-03-11</t>
-        </is>
-      </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2026-01-31 · shares · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="30" t="n">
         <v>4</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -2262,24 +2408,24 @@
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2023-12-30 · shares · filed 2026-01-23</t>
-        </is>
-      </c>
-      <c r="E11" s="29" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-12-27 · shares · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="30" t="n">
         <v>5</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -2287,24 +2433,24 @@
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2024-12-28 · USD · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:LongTermDebtNoncurrent · period ending 2025-12-27 · USD · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="30" t="n">
         <v>6</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -2312,24 +2458,24 @@
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2024-11-03 · USD · filed 2025-12-18</t>
-        </is>
-      </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2025-11-02 · USD · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="30" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -2337,24 +2483,24 @@
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2025-02-01 · USD · filed 2026-03-11</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:LongTermDebtNoncurrent · period ending 2026-01-31 · USD · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F14" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="30" t="n">
         <v>8</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -2362,24 +2508,24 @@
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2024-12-28 · USD · filed 2026-01-23</t>
-        </is>
-      </c>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:LongTermDebtNoncurrent · period ending 2025-12-27 · USD · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="30" t="n">
         <v>9</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -2387,24 +2533,24 @@
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D16" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2023-12-30 · USD · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E16" s="29" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-12-27 · USD · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="30" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -2412,24 +2558,24 @@
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2024-11-03 · USD · filed 2025-12-18</t>
-        </is>
-      </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-11-02 · USD · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="30" t="n">
         <v>11</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -2437,24 +2583,24 @@
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-02-01 · USD · filed 2026-03-11</t>
-        </is>
-      </c>
-      <c r="E18" s="29" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2026-01-31 · USD · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="30" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -2462,24 +2608,24 @@
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2024-12-28 · USD · filed 2026-01-23</t>
-        </is>
-      </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-12-27 · USD · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr">
+      <c r="F19" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="30" t="n">
         <v>13</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -2487,24 +2633,24 @@
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:ShortTermInvestments · period ending 2024-12-28 · USD · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E20" s="29" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:ShortTermInvestments · period ending 2025-12-27 · USD · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F20" s="30" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="30" t="n">
         <v>14</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -2512,24 +2658,24 @@
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:AvailableForSaleSecuritiesDebtSecuritiesCurrent · period ending 2024-12-28 · USD · filed 2026-01-23</t>
-        </is>
-      </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:AvailableForSaleSecuritiesDebtSecuritiesCurrent · period ending 2025-12-27 · USD · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr">
+      <c r="F21" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="30" t="n">
         <v>15</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2537,24 +2683,24 @@
           <t>NVDA FY2022 10-K</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2020-01-26 · USD · filed 2022-03-18</t>
-        </is>
-      </c>
-      <c r="E22" s="29" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2022-01-30 · USD · filed 2022-03-18</t>
+        </is>
+      </c>
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>0001045810-22-000036</t>
         </is>
       </c>
-      <c r="F22" s="30" t="inlineStr">
+      <c r="F22" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581022000036/0001045810-22-000036-index.htm</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="30" t="n">
         <v>16</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -2562,24 +2708,24 @@
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D23" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2023-12-30 · USD · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E23" s="29" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-12-27 · USD · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F23" s="30" t="inlineStr">
+      <c r="F23" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="30" t="n">
         <v>17</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -2587,24 +2733,24 @@
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2023-10-29 · USD · filed 2025-12-18</t>
-        </is>
-      </c>
-      <c r="E24" s="29" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-11-02 · USD · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F24" s="30" t="inlineStr">
+      <c r="F24" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="30" t="n">
         <v>18</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2612,24 +2758,24 @@
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D25" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2024-02-03 · USD · filed 2026-03-11</t>
-        </is>
-      </c>
-      <c r="E25" s="29" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2026-01-31 · USD · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F25" s="30" t="inlineStr">
+      <c r="F25" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="30" t="n">
         <v>19</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -2637,24 +2783,24 @@
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2023-12-30 · USD · filed 2026-01-23</t>
-        </is>
-      </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-12-27 · USD · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F26" s="30" t="inlineStr">
+      <c r="F26" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="30" t="n">
         <v>20</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2662,24 +2808,24 @@
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:GrossProfit · period ending 2023-12-30 · USD · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E27" s="29" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:GrossProfit · period ending 2025-12-27 · USD · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="30" t="n">
         <v>21</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -2687,24 +2833,24 @@
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:GrossProfit · period ending 2023-10-29 · USD · filed 2025-12-18</t>
-        </is>
-      </c>
-      <c r="E28" s="29" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:GrossProfit · period ending 2025-11-02 · USD · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F28" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="30" t="n">
         <v>22</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -2712,24 +2858,24 @@
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:GrossProfit · period ending 2024-02-03 · USD · filed 2026-03-11</t>
-        </is>
-      </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:GrossProfit · period ending 2026-01-31 · USD · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="30" t="n">
         <v>23</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -2737,24 +2883,24 @@
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:GrossProfit · period ending 2023-12-30 · USD · filed 2026-01-23</t>
-        </is>
-      </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:GrossProfit · period ending 2025-12-27 · USD · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F30" s="30" t="inlineStr">
+      <c r="F30" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="30" t="n">
         <v>24</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -2762,24 +2908,24 @@
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D31" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:OperatingIncomeLoss · period ending 2023-12-30 · USD · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E31" s="29" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2025-12-27 · USD · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="29" t="n">
+      <c r="B32" s="30" t="n">
         <v>25</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -2787,24 +2933,24 @@
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D32" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:OperatingIncomeLoss · period ending 2023-10-29 · USD · filed 2025-12-18</t>
-        </is>
-      </c>
-      <c r="E32" s="29" t="inlineStr">
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2025-11-02 · USD · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E32" s="30" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
+      <c r="F32" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="30" t="n">
         <v>26</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -2812,24 +2958,24 @@
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D33" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:OperatingIncomeLoss · period ending 2024-02-03 · USD · filed 2026-03-11</t>
-        </is>
-      </c>
-      <c r="E33" s="29" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2026-01-31 · USD · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="30" t="n">
         <v>27</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -2837,24 +2983,24 @@
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D34" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:OperatingIncomeLoss · period ending 2023-12-30 · USD · filed 2026-01-23</t>
-        </is>
-      </c>
-      <c r="E34" s="29" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2025-12-27 · USD · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F34" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="30" t="n">
         <v>28</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -2862,24 +3008,24 @@
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D35" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2023-12-30 · USD · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E35" s="29" t="inlineStr">
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:NetIncomeLoss · period ending 2025-12-27 · USD · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F35" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="30" t="n">
         <v>29</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -2887,24 +3033,24 @@
           <t>AVGO FY2024 10-K</t>
         </is>
       </c>
-      <c r="D36" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2022-10-30 · USD · filed 2024-12-20</t>
-        </is>
-      </c>
-      <c r="E36" s="29" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:NetIncomeLoss · period ending 2024-11-03 · USD · filed 2024-12-20</t>
+        </is>
+      </c>
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>0001730168-24-000139</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="F36" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016824000139/0001730168-24-000139-index.htm</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="30" t="n">
         <v>30</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -2912,24 +3058,24 @@
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D37" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2024-02-03 · USD · filed 2026-03-11</t>
-        </is>
-      </c>
-      <c r="E37" s="29" t="inlineStr">
+      <c r="D37" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:NetIncomeLoss · period ending 2026-01-31 · USD · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F37" s="30" t="inlineStr">
+      <c r="F37" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="30" t="n">
         <v>31</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -2937,24 +3083,24 @@
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D38" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2023-12-30 · USD · filed 2026-01-23</t>
-        </is>
-      </c>
-      <c r="E38" s="29" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:NetIncomeLoss · period ending 2025-12-27 · USD · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
+      <c r="F38" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="29" t="n">
+      <c r="B39" s="30" t="n">
         <v>32</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -2962,24 +3108,24 @@
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D39" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:EarningsPerShareDiluted · period ending 2023-12-30 · USD/shares · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E39" s="29" t="inlineStr">
+      <c r="D39" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2025-12-27 · USD/shares · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E39" s="30" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
+      <c r="F39" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="30" t="n">
         <v>33</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -2987,24 +3133,24 @@
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D40" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:EarningsPerShareDiluted · period ending 2023-10-29 · USD/shares · filed 2025-12-18</t>
-        </is>
-      </c>
-      <c r="E40" s="29" t="inlineStr">
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2025-11-02 · USD/shares · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F40" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="29" t="n">
+      <c r="B41" s="30" t="n">
         <v>34</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -3012,24 +3158,24 @@
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D41" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:EarningsPerShareDiluted · period ending 2024-02-03 · USD/shares · filed 2026-03-11</t>
-        </is>
-      </c>
-      <c r="E41" s="29" t="inlineStr">
+      <c r="D41" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2026-01-31 · USD/shares · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E41" s="30" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="29" t="n">
+      <c r="B42" s="30" t="n">
         <v>35</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3037,17 +3183,17 @@
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D42" s="29" t="inlineStr">
-        <is>
-          <t>us-gaap:EarningsPerShareDiluted · period ending 2023-12-30 · USD/shares · filed 2026-01-23</t>
-        </is>
-      </c>
-      <c r="E42" s="29" t="inlineStr">
+      <c r="D42" s="30" t="inlineStr">
+        <is>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2025-12-27 · USD/shares · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E42" s="30" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F42" s="30" t="inlineStr">
+      <c r="F42" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,25 +160,19 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -688,52 +682,50 @@
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="n">
+      <c r="D9" s="11" t="n">
+        <v>24514000000</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>1636000000</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="11" t="n">
         <v>4853000000</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="11" t="n">
         <v>869700000</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="11" t="n">
         <v>4530000000</v>
       </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>[1][2][3][4]</t>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>[1][2][3][4][5]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <f>IFERROR(D8*D9,"")</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <f>IFERROR(E8*E9,"")</f>
         <v/>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <f>IFERROR(F8*F9,"")</f>
         <v/>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="14">
         <f>IFERROR(G8*G9,"")</f>
         <v/>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="14">
         <f>IFERROR(H8*H9,"")</f>
         <v/>
       </c>
@@ -756,26 +748,24 @@
           <t>Total debt</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>3222000000</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>3152000000</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>3970800000</v>
-      </c>
-      <c r="H13" s="17" t="n">
+      <c r="D13" s="15" t="n">
+        <v>9467000000</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>4124000000</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>70272000000</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>4470600000</v>
+      </c>
+      <c r="H13" s="15" t="n">
         <v>46585000000</v>
       </c>
-      <c r="J13" s="13" t="inlineStr">
-        <is>
-          <t>[5][6][7][8]</t>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>[6][7][8][9][10]</t>
         </is>
       </c>
     </row>
@@ -785,26 +775,24 @@
           <t>Cash and equivalents</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="n">
+      <c r="D14" s="15" t="n">
+        <v>10605000000</v>
+      </c>
+      <c r="E14" s="15" t="n">
         <v>5539000000</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="15" t="n">
         <v>16178000000</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="15" t="n">
         <v>2638800000</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="15" t="n">
         <v>14265000000</v>
       </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>[9][10][11][12]</t>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>[11][12][13][14][15]</t>
         </is>
       </c>
     </row>
@@ -814,12 +802,10 @@
           <t>Short-term investments</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n">
+      <c r="D15" s="15" t="n">
+        <v>34621000000</v>
+      </c>
+      <c r="E15" s="15" t="n">
         <v>5013000000</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -832,65 +818,65 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H15" s="15" t="n">
         <v>23151000000</v>
       </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>[13][14]</t>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>[16][17][18]</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Net debt / (net cash)</t>
         </is>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <f>IFERROR(D13-D14-D15,"")</f>
         <v/>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <f>IFERROR(E13-E14-E15,"")</f>
         <v/>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <f>IFERROR(F13-F14-F15,"")</f>
         <v/>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <f>IFERROR(G13-G14-G15,"")</f>
         <v/>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="14">
         <f>IFERROR(H13-H14-H15,"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <f>IFERROR(D10+D16,"")</f>
         <v/>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <f>IFERROR(E10+E16,"")</f>
         <v/>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="14">
         <f>IFERROR(F10+F16,"")</f>
         <v/>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="14">
         <f>IFERROR(G10+G16,"")</f>
         <v/>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="14">
         <f>IFERROR(H10+H16,"")</f>
         <v/>
       </c>
@@ -908,64 +894,64 @@
       <c r="H19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Fiscal year end</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Period covered</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="18" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="H21" s="18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -977,24 +963,24 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n">
-        <v>26914000000</v>
-      </c>
-      <c r="E22" s="17" t="n">
+      <c r="D22" s="15" t="n">
+        <v>215938000000</v>
+      </c>
+      <c r="E22" s="15" t="n">
         <v>34639000000</v>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="F22" s="15" t="n">
         <v>63887000000</v>
       </c>
-      <c r="G22" s="17" t="n">
+      <c r="G22" s="15" t="n">
         <v>8194600000</v>
       </c>
-      <c r="H22" s="17" t="n">
+      <c r="H22" s="15" t="n">
         <v>52853000000</v>
       </c>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>[15][16][17][18][19]</t>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>[19][20][21][22][23]</t>
         </is>
       </c>
     </row>
@@ -1004,52 +990,50 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="n">
+      <c r="D23" s="15" t="n">
+        <v>153463000000</v>
+      </c>
+      <c r="E23" s="15" t="n">
         <v>17152000000</v>
       </c>
-      <c r="F23" s="17" t="n">
+      <c r="F23" s="15" t="n">
         <v>43294000000</v>
       </c>
-      <c r="G23" s="17" t="n">
+      <c r="G23" s="15" t="n">
         <v>4180700000</v>
       </c>
-      <c r="H23" s="17" t="n">
+      <c r="H23" s="15" t="n">
         <v>18375000000</v>
       </c>
-      <c r="J23" s="13" t="inlineStr">
-        <is>
-          <t>[20][21][22][23]</t>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>[24][25][26][27][28]</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">    % gross margin</t>
         </is>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="19">
         <f>IFERROR(D23/D22,"")</f>
         <v/>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="19">
         <f>IFERROR(E23/E22,"")</f>
         <v/>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="19">
         <f>IFERROR(F23/F22,"")</f>
         <v/>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="19">
         <f>IFERROR(G23/G22,"")</f>
         <v/>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="19">
         <f>IFERROR(H23/H22,"")</f>
         <v/>
       </c>
@@ -1060,26 +1044,24 @@
           <t>Operating income</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="n">
+      <c r="D25" s="15" t="n">
+        <v>130387000000</v>
+      </c>
+      <c r="E25" s="15" t="n">
         <v>3694000000</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="15" t="n">
         <v>25484000000</v>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G25" s="15" t="n">
         <v>1322900000</v>
       </c>
-      <c r="H25" s="17" t="n">
+      <c r="H25" s="15" t="n">
         <v>-2214000000</v>
       </c>
-      <c r="J25" s="13" t="inlineStr">
-        <is>
-          <t>[24][25][26][27]</t>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>[29][30][31][32][33]</t>
         </is>
       </c>
     </row>
@@ -1089,82 +1071,77 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D26" s="15" t="n">
+        <v>2400000000</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>521000000</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>574000000</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>221700000</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>10757000000</v>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>[34][35][36][37][38]</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <f>IFERROR(D25+D26,"")</f>
         <v/>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="14">
         <f>IFERROR(E25+E26,"")</f>
         <v/>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="14">
         <f>IFERROR(F25+F26,"")</f>
         <v/>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="14">
         <f>IFERROR(G25+G26,"")</f>
         <v/>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="14">
         <f>IFERROR(H25+H26,"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">    % EBITDA margin</t>
         </is>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="19">
         <f>IFERROR(D27/D22,"")</f>
         <v/>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="19">
         <f>IFERROR(E27/E22,"")</f>
         <v/>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="19">
         <f>IFERROR(F27/F22,"")</f>
         <v/>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="19">
         <f>IFERROR(G27/G22,"")</f>
         <v/>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="19">
         <f>IFERROR(H27/H22,"")</f>
         <v/>
       </c>
@@ -1175,26 +1152,24 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="n">
+      <c r="D29" s="15" t="n">
+        <v>120067000000</v>
+      </c>
+      <c r="E29" s="15" t="n">
         <v>4335000000</v>
       </c>
-      <c r="F29" s="17" t="n">
-        <v>5895000000</v>
-      </c>
-      <c r="G29" s="17" t="n">
+      <c r="F29" s="15" t="n">
+        <v>23126000000</v>
+      </c>
+      <c r="G29" s="15" t="n">
         <v>2670100000</v>
       </c>
-      <c r="H29" s="17" t="n">
+      <c r="H29" s="15" t="n">
         <v>-267000000</v>
       </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>[28][29][30][31]</t>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>[39][40][41][42][43]</t>
         </is>
       </c>
     </row>
@@ -1204,26 +1179,24 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="n">
+      <c r="D30" s="20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E30" s="20" t="n">
         <v>2.65</v>
       </c>
-      <c r="F30" s="22" t="n">
+      <c r="F30" s="20" t="n">
         <v>4.77</v>
       </c>
-      <c r="G30" s="22" t="n">
+      <c r="G30" s="20" t="n">
         <v>3.07</v>
       </c>
-      <c r="H30" s="22" t="n">
+      <c r="H30" s="20" t="n">
         <v>-0.06</v>
       </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>[32][33][34][35]</t>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>[44][45][46][47][48]</t>
         </is>
       </c>
     </row>
@@ -1245,23 +1218,23 @@
           <t>EV / Revenue</t>
         </is>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="21">
         <f>IFERROR(D17/D22,"")</f>
         <v/>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="21">
         <f>IFERROR(E17/E22,"")</f>
         <v/>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="21">
         <f>IFERROR(F17/F22,"")</f>
         <v/>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="21">
         <f>IFERROR(G17/G22,"")</f>
         <v/>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="21">
         <f>IFERROR(H17/H22,"")</f>
         <v/>
       </c>
@@ -1272,23 +1245,23 @@
           <t>EV / EBITDA</t>
         </is>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="21">
         <f>IFERROR(D17/D27,"")</f>
         <v/>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="21">
         <f>IFERROR(E17/E27,"")</f>
         <v/>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="21">
         <f>IFERROR(F17/F27,"")</f>
         <v/>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="21">
         <f>IFERROR(G17/G27,"")</f>
         <v/>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="21">
         <f>IFERROR(H17/H27,"")</f>
         <v/>
       </c>
@@ -1299,23 +1272,23 @@
           <t>P / E</t>
         </is>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="21">
         <f>IFERROR(D8/D30,"")</f>
         <v/>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="21">
         <f>IFERROR(E8/E30,"")</f>
         <v/>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="21">
         <f>IFERROR(F8/F30,"")</f>
         <v/>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="21">
         <f>IFERROR(G8/G30,"")</f>
         <v/>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="21">
         <f>IFERROR(H8/H30,"")</f>
         <v/>
       </c>
@@ -1338,27 +1311,27 @@
           <t>NTM revenue (input)</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="24" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1370,27 +1343,27 @@
           <t>NTM EBITDA (input)</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="24" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1434,23 +1407,23 @@
           <t>EV / NTM revenue</t>
         </is>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="21">
         <f>IFERROR(D17/D38,"")</f>
         <v/>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="21">
         <f>IFERROR(E17/E38,"")</f>
         <v/>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="21">
         <f>IFERROR(F17/F38,"")</f>
         <v/>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="21">
         <f>IFERROR(G17/G38,"")</f>
         <v/>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="21">
         <f>IFERROR(H17/H38,"")</f>
         <v/>
       </c>
@@ -1461,23 +1434,23 @@
           <t>EV / NTM EBITDA</t>
         </is>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="21">
         <f>IFERROR(D17/D39,"")</f>
         <v/>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="21">
         <f>IFERROR(E17/E39,"")</f>
         <v/>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="21">
         <f>IFERROR(F17/F39,"")</f>
         <v/>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="21">
         <f>IFERROR(G17/G39,"")</f>
         <v/>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="21">
         <f>IFERROR(H17/H39,"")</f>
         <v/>
       </c>
@@ -1488,23 +1461,23 @@
           <t>Forward P / E</t>
         </is>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="21">
         <f>IFERROR(D8/D40,"")</f>
         <v/>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="21">
         <f>IFERROR(E8/E40,"")</f>
         <v/>
       </c>
-      <c r="F43" s="23">
+      <c r="F43" s="21">
         <f>IFERROR(F8/F40,"")</f>
         <v/>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="21">
         <f>IFERROR(G8/G40,"")</f>
         <v/>
       </c>
-      <c r="H43" s="23">
+      <c r="H43" s="21">
         <f>IFERROR(H8/H40,"")</f>
         <v/>
       </c>
@@ -1522,393 +1495,393 @@
       <c r="H45" s="8" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>Trailing EV / Revenue — median</t>
         </is>
       </c>
-      <c r="D46" s="25">
+      <c r="D46" s="23">
         <f>IFERROR(MEDIAN(D33:H33),"")</f>
         <v/>
       </c>
-      <c r="E46" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="26" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>Trailing EV / Revenue — mean</t>
         </is>
       </c>
-      <c r="D47" s="25">
+      <c r="D47" s="23">
         <f>IFERROR(AVERAGE(D33:H33),"")</f>
         <v/>
       </c>
-      <c r="E47" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="26" t="inlineStr">
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>Trailing EV / EBITDA — median</t>
         </is>
       </c>
-      <c r="D48" s="25">
+      <c r="D48" s="23">
         <f>IFERROR(MEDIAN(D34:H34),"")</f>
         <v/>
       </c>
-      <c r="E48" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F48" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="26" t="inlineStr">
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>Trailing EV / EBITDA — mean</t>
         </is>
       </c>
-      <c r="D49" s="25">
+      <c r="D49" s="23">
         <f>IFERROR(AVERAGE(D34:H34),"")</f>
         <v/>
       </c>
-      <c r="E49" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="26" t="inlineStr">
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>Trailing P / E — median</t>
         </is>
       </c>
-      <c r="D50" s="25">
+      <c r="D50" s="23">
         <f>IFERROR(MEDIAN(D35:H35),"")</f>
         <v/>
       </c>
-      <c r="E50" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="26" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>Trailing P / E — mean</t>
         </is>
       </c>
-      <c r="D51" s="25">
+      <c r="D51" s="23">
         <f>IFERROR(AVERAGE(D35:H35),"")</f>
         <v/>
       </c>
-      <c r="E51" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="26" t="inlineStr">
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>Forward EV / Revenue — median</t>
         </is>
       </c>
-      <c r="D52" s="25">
+      <c r="D52" s="23">
         <f>IFERROR(MEDIAN(D41:H41),"")</f>
         <v/>
       </c>
-      <c r="E52" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="26" t="inlineStr">
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>Forward EV / Revenue — mean</t>
         </is>
       </c>
-      <c r="D53" s="25">
+      <c r="D53" s="23">
         <f>IFERROR(AVERAGE(D41:H41),"")</f>
         <v/>
       </c>
-      <c r="E53" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="26" t="inlineStr">
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>Forward EV / EBITDA — median</t>
         </is>
       </c>
-      <c r="D54" s="25">
+      <c r="D54" s="23">
         <f>IFERROR(MEDIAN(D42:H42),"")</f>
         <v/>
       </c>
-      <c r="E54" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="26" t="inlineStr">
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>Forward EV / EBITDA — mean</t>
         </is>
       </c>
-      <c r="D55" s="25">
+      <c r="D55" s="23">
         <f>IFERROR(AVERAGE(D42:H42),"")</f>
         <v/>
       </c>
-      <c r="E55" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="26" t="inlineStr">
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>Forward P / E — median</t>
         </is>
       </c>
-      <c r="D56" s="25">
+      <c r="D56" s="23">
         <f>IFERROR(MEDIAN(D43:H43),"")</f>
         <v/>
       </c>
-      <c r="E56" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="26" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>Forward P / E — mean</t>
         </is>
       </c>
-      <c r="D57" s="25">
+      <c r="D57" s="23">
         <f>IFERROR(AVERAGE(D43:H43),"")</f>
         <v/>
       </c>
-      <c r="E57" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="26" t="inlineStr">
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="27" t="inlineStr">
+      <c r="B59" s="25" t="inlineStr">
         <is>
           <t>Shaded blue cells are yours to fill: price and consensus are not filing data, so this workbook will not guess them.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="27" t="inlineStr">
+      <c r="B60" s="25" t="inlineStr">
         <is>
           <t>Multiples recompute from the cells above. Never hard-code a multiple.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="27" t="inlineStr">
+      <c r="B61" s="25" t="inlineStr">
         <is>
           <t>CALENDARISATION REQUIRED: these filers do not share a fiscal year end (Dec, Jan, Nov). The multiples above compare different twelve-month windows. Calendarise to a common year end before using them, and say in the footnote which filers were adjusted and how.</t>
         </is>
@@ -1958,7 +1931,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Fill the rationale column before you show this to anyone. Business-model similarity, size band, growth band, margin structure and end-market exposure are the five tests that survive scrutiny.</t>
         </is>
@@ -1970,7 +1943,7 @@
           <t>NVDA — NVIDIA CORP</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -1982,7 +1955,7 @@
           <t>AMD — ADVANCED MICRO DEVICES INC</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -1994,7 +1967,7 @@
           <t>AVGO — Broadcom Inc.</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -2006,7 +1979,7 @@
           <t>MRVL — Marvell Technology, Inc.</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -2018,7 +1991,7 @@
           <t>INTC — INTEL CORP</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
@@ -2032,7 +2005,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>An empty rejection list is a red flag. If you did not reject anyone, you did not build a set, you took a sector list.</t>
         </is>
@@ -2044,7 +2017,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2056,7 +2029,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2068,7 +2041,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2080,7 +2053,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2092,7 +2065,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2104,7 +2077,7 @@
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
@@ -2123,9 +2096,9 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
-        <is>
-          <t>Fiscal year ends Jan · latest period FY2022</t>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Fiscal year ends Jan · latest period FY2026</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2108,7 @@
           <t>AMD</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>Fiscal year ends Dec · latest period FY2025</t>
         </is>
@@ -2147,7 +2120,7 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>Fiscal year ends Nov · latest period FY2025</t>
         </is>
@@ -2159,7 +2132,7 @@
           <t>MRVL</t>
         </is>
       </c>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>Fiscal year ends Jan · latest period FY2026</t>
         </is>
@@ -2171,14 +2144,14 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>Fiscal year ends Dec · latest period FY2025</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="27" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>Year ends differ across the set. State the common year end you calendarised to and which filers were stubbed, or the comparison is not a comparison.</t>
         </is>
@@ -2192,7 +2165,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>Note every adjustment here: stock-based compensation treatment, operating leases capitalised or not, non-recurring items excluded, fiscal-year calendarisation. An unstated adjustment is the fastest way to lose the room.</t>
         </is>
@@ -2204,7 +2177,7 @@
           <t>[adjustment]</t>
         </is>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>[what and why]</t>
         </is>
@@ -2216,7 +2189,7 @@
           <t>[adjustment]</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D36" s="26" t="inlineStr">
         <is>
           <t>[what and why]</t>
         </is>
@@ -2228,7 +2201,7 @@
           <t>[adjustment]</t>
         </is>
       </c>
-      <c r="D37" s="28" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>[what and why]</t>
         </is>
@@ -2240,7 +2213,7 @@
           <t>[adjustment]</t>
         </is>
       </c>
-      <c r="D38" s="28" t="inlineStr">
+      <c r="D38" s="26" t="inlineStr">
         <is>
           <t>[what and why]</t>
         </is>
@@ -2258,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F42"/>
+  <dimension ref="B2:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2291,7 +2264,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Share price and forward consensus are user inputs and carry no filing provenance by design.</t>
         </is>
@@ -2325,875 +2298,1200 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
+          <t>NVDA FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2026-01-25 · shares · filed 2026-02-25</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-26-000021</t>
+        </is>
+      </c>
+      <c r="F8" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-12-27 · shares · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-11-02 · shares · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2026-01-31 · shares · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-12-27 · shares · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NVDA FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:LongTermDebt · period ending 2026-01-25 · USD · filed 2026-02-25</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-26-000021</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr">
-        <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2025-12-27 · USD · filed 2026-02-04</t>
-        </is>
-      </c>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2025-12-27 · USD · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2025-11-02 · USD · filed 2025-12-18</t>
-        </is>
-      </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2025-11-02 · USD · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D14" s="30" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebtNoncurrent · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D15" s="30" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebtNoncurrent · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>NVDA FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2026-01-25 · USD · filed 2026-02-25</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-26-000021</t>
+        </is>
+      </c>
+      <c r="F18" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D16" s="30" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E16" s="30" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E17" s="30" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr">
+      <c r="F20" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
-        <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2026-01-31 · USD · filed 2026-03-11</t>
-        </is>
-      </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:CashCashEquivalentsRestrictedCashAndRestrictedCashEquivalents · period ending 2026-01-31 · USD · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D19" s="30" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E19" s="30" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="F22" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="30" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>NVDA FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:MarketableSecuritiesCurrent · period ending 2025-01-26 · USD · filed 2025-02-26</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-25-000023</t>
+        </is>
+      </c>
+      <c r="F23" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581025000023/0001045810-25-000023-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D20" s="30" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>us-gaap:ShortTermInvestments · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E20" s="30" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F20" s="31" t="inlineStr">
+      <c r="F24" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>us-gaap:AvailableForSaleSecuritiesDebtSecuritiesCurrent · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E21" s="30" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr">
+      <c r="F25" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>NVDA FY2022 10-K</t>
-        </is>
-      </c>
-      <c r="D22" s="30" t="inlineStr">
-        <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2022-01-30 · USD · filed 2022-03-18</t>
-        </is>
-      </c>
-      <c r="E22" s="30" t="inlineStr">
-        <is>
-          <t>0001045810-22-000036</t>
-        </is>
-      </c>
-      <c r="F22" s="31" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581022000036/0001045810-22-000036-index.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>NVDA FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:Revenues · period ending 2026-01-25 · USD · filed 2026-02-25</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-26-000021</t>
+        </is>
+      </c>
+      <c r="F26" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D23" s="30" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E23" s="30" t="inlineStr">
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F23" s="31" t="inlineStr">
+      <c r="F27" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="30" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F24" s="31" t="inlineStr">
+      <c r="F28" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D25" s="30" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E25" s="30" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr">
+      <c r="F29" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D26" s="30" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F26" s="31" t="inlineStr">
+      <c r="F30" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>NVDA FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:GrossProfit · period ending 2026-01-25 · USD · filed 2026-02-25</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-26-000021</t>
+        </is>
+      </c>
+      <c r="F31" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D27" s="30" t="inlineStr">
+      <c r="D32" s="28" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E27" s="30" t="inlineStr">
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F27" s="31" t="inlineStr">
+      <c r="F32" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="30" t="n">
-        <v>21</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D28" s="30" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E28" s="30" t="inlineStr">
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F28" s="31" t="inlineStr">
+      <c r="F33" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="30" t="n">
-        <v>22</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E29" s="30" t="inlineStr">
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr">
+      <c r="F34" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="30" t="n">
-        <v>23</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="D35" s="28" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E35" s="28" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F30" s="31" t="inlineStr">
+      <c r="F35" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>NVDA FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2026-01-25 · USD · filed 2026-02-25</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-26-000021</t>
+        </is>
+      </c>
+      <c r="F36" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
+      <c r="D37" s="28" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F31" s="31" t="inlineStr">
+      <c r="F37" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D32" s="30" t="inlineStr">
+      <c r="D38" s="28" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E32" s="30" t="inlineStr">
+      <c r="E38" s="28" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F32" s="31" t="inlineStr">
+      <c r="F38" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="30" t="n">
-        <v>26</v>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D33" s="30" t="inlineStr">
+      <c r="D39" s="28" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E33" s="30" t="inlineStr">
+      <c r="E39" s="28" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F33" s="31" t="inlineStr">
+      <c r="F39" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="30" t="n">
-        <v>27</v>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D34" s="30" t="inlineStr">
+      <c r="D40" s="28" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="E40" s="28" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F34" s="31" t="inlineStr">
+      <c r="F40" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="30" t="n">
-        <v>28</v>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>NVDA FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D41" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:Depreciation · period ending 2026-01-25 · USD · filed 2026-02-25</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-26-000021</t>
+        </is>
+      </c>
+      <c r="F41" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
+      <c r="D42" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:Depreciation · period ending 2025-12-27 · USD · filed 2026-02-04</t>
+        </is>
+      </c>
+      <c r="E42" s="28" t="inlineStr">
+        <is>
+          <t>0000002488-26-000018</t>
+        </is>
+      </c>
+      <c r="F42" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>AVGO FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="D43" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:Depreciation · period ending 2025-11-02 · USD · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
+        <is>
+          <t>0001730168-25-000121</t>
+        </is>
+      </c>
+      <c r="F43" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>MRVL FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D44" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:Depreciation · period ending 2026-01-31 · USD · filed 2026-03-11</t>
+        </is>
+      </c>
+      <c r="E44" s="28" t="inlineStr">
+        <is>
+          <t>0001835632-26-000011</t>
+        </is>
+      </c>
+      <c r="F44" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>INTC FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="D45" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:Depreciation · period ending 2025-12-27 · USD · filed 2026-01-23</t>
+        </is>
+      </c>
+      <c r="E45" s="28" t="inlineStr">
+        <is>
+          <t>0000050863-26-000011</t>
+        </is>
+      </c>
+      <c r="F45" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="28" t="n">
+        <v>39</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NVDA FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D46" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:NetIncomeLoss · period ending 2026-01-25 · USD · filed 2026-02-25</t>
+        </is>
+      </c>
+      <c r="E46" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-26-000021</t>
+        </is>
+      </c>
+      <c r="F46" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>AMD FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="D47" s="28" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="E47" s="28" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr">
+      <c r="F47" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="30" t="n">
-        <v>29</v>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>AVGO FY2024 10-K</t>
-        </is>
-      </c>
-      <c r="D36" s="30" t="inlineStr">
-        <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2024-11-03 · USD · filed 2024-12-20</t>
-        </is>
-      </c>
-      <c r="E36" s="30" t="inlineStr">
-        <is>
-          <t>0001730168-24-000139</t>
-        </is>
-      </c>
-      <c r="F36" s="31" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016824000139/0001730168-24-000139-index.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="28" t="n">
+        <v>41</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>AVGO FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:ProfitLoss · period ending 2025-11-02 · USD · filed 2025-12-18</t>
+        </is>
+      </c>
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>0001730168-25-000121</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D37" s="30" t="inlineStr">
+      <c r="D49" s="28" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E37" s="30" t="inlineStr">
+      <c r="E49" s="28" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F37" s="31" t="inlineStr">
+      <c r="F49" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="30" t="n">
-        <v>31</v>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D38" s="30" t="inlineStr">
+      <c r="D50" s="28" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E38" s="30" t="inlineStr">
+      <c r="E50" s="28" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F38" s="31" t="inlineStr">
+      <c r="F50" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="28" t="n">
+        <v>44</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>NVDA FY2026 10-K</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="inlineStr">
+        <is>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2026-01-25 · USD/shares · filed 2026-02-25</t>
+        </is>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>0001045810-26-000021</t>
+        </is>
+      </c>
+      <c r="F51" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D39" s="30" t="inlineStr">
+      <c r="D52" s="28" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2025-12-27 · USD/shares · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E39" s="30" t="inlineStr">
+      <c r="E52" s="28" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F39" s="31" t="inlineStr">
+      <c r="F52" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="30" t="n">
-        <v>33</v>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="28" t="n">
+        <v>46</v>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D40" s="30" t="inlineStr">
+      <c r="D53" s="28" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2025-11-02 · USD/shares · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E53" s="28" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F40" s="31" t="inlineStr">
+      <c r="F53" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="30" t="n">
-        <v>34</v>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="28" t="n">
+        <v>47</v>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D41" s="30" t="inlineStr">
+      <c r="D54" s="28" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2026-01-31 · USD/shares · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E41" s="30" t="inlineStr">
+      <c r="E54" s="28" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F41" s="31" t="inlineStr">
+      <c r="F54" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D42" s="30" t="inlineStr">
+      <c r="D55" s="28" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2025-12-27 · USD/shares · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E42" s="30" t="inlineStr">
+      <c r="E55" s="28" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F42" s="31" t="inlineStr">
+      <c r="F55" s="29" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
@@ -3236,6 +3534,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -7,13 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Comps" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Inclusion" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sources" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Comps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inclusion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sources" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Comps'!$B$2:$J$62</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inclusion'!$B$2:$F$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Comps'!$A$1:$J$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Inclusion'!$A$1:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +30,7 @@
     <numFmt numFmtId="167" formatCode="0.0%_);\(0.0%\)"/>
     <numFmt numFmtId="168" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,8 +115,22 @@
       <sz val="9"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF264D82"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF333333"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -124,6 +140,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,8 +165,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -154,8 +187,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -170,7 +201,6 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -261,6 +291,126 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1628775" cy="304800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="971550" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="971550" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="971550" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -552,7 +702,300 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J61"/>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="10" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="10" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Trading Comparables — NVDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Produced by the L3VLUP Comps Set Builder skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Generated 24 August 2026 at 11:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>What this is</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>A trading-comparables sheet for NVDA against 4 peers. Fundamentals come from each filer’s own filings; every multiple, median and mean is a live formula, so changing one price moves the whole sheet. The Inclusion tab is the part that matters: fill in why each name belongs, which names you rejected, and every adjustment you made, before showing this to anyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>BLUE  —  a hard input, or a value pulled straight from a filing. Something a human can change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>BLACK  —  a formula computed inside this workbook. Do not overtype it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>GREEN  —  a link to another sheet in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>RED FILL  —  a tie-out that failed. Investigate before using the workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>AN EM DASH  —  the filer did not tag that line. It does not mean zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Every [n] marker beside a row resolves on the Sources tab to a tag, a period, a form and an accession number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Where the numbers come from</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="65" customHeight="1">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Revenue, EBITDA inputs, debt, cash and share counts come from each company’s SEC filings. Share price and forward consensus are NOT filing data: they are shaded input cells for you to fill from your own licensed feed. The workbook will not guess a price and then print a multiple off it. EBITDA is built in the sheet from operating income plus D&amp;A, because EBITDA is not a GAAP tag and any figure claiming to be one is somebody’s adjustment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Important notices</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="39" customHeight="1">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>EDUCATIONAL USE ONLY. This workbook is produced by L3VLUP as a training and learning aid. It is not investment research, not a recommendation, and not an offer or solicitation to buy or sell any security or financial instrument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="39" customHeight="1">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>NOT INVESTMENT, LEGAL, TAX OR ACCOUNTING ADVICE. Nothing in this file constitutes advice of any kind and it takes no account of the objectives, financial situation or needs of any person. Obtain advice from a suitably qualified and regulated professional before acting on anything here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>NO RELIANCE. The figures are assembled automatically from third-party filings and may be incomplete, mis-tagged at source, superseded by a later restatement, or wrong. Independently verify every figure against the underlying filing — which is why each one is linked — before relying on it for any purpose. Past performance is not a guide to future performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>NO WARRANTY. This workbook is provided “as is” and “as available”, without warranty of any kind, express or implied, including any warranty of accuracy, completeness, merchantability or fitness for a particular purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="65" customHeight="1">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>LIMITATION OF LIABILITY. To the fullest extent permitted by law, L3VLUP and its officers, employees and contributors accept no liability for any loss or damage — including any direct, indirect, incidental, consequential or economic loss, loss of profit, or loss of data — arising out of or in connection with the use of, or reliance on, this workbook or anything in it. Nothing in this notice limits or excludes any liability that cannot lawfully be limited or excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>THIRD-PARTY DATA. Filing data originates from the U.S. Securities and Exchange Commission’s EDGAR system and is in the public domain. The SEC does not endorse, sponsor or verify this workbook. Any figures you enter yourself remain governed by the terms of whichever data provider supplied them, and it is your responsibility to hold the necessary licence for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Copyright</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>© 2026 L3VLUP. All rights reserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>The structure, layout, formulas, wording and conventions of this workbook are the property of L3VLUP. It is licensed to the named recipient for their own personal study and professional work. You may not resell it, redistribute it, publish it, or use it to build or train a competing product or dataset, in whole or in part, without prior written permission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Underlying filing data is public domain and is not claimed as L3VLUP property.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>l3vlup.com  ·  l3vlup.com/skills/comps-set-builder</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B28:H28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -567,1321 +1010,1357 @@
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>NVDA comparable companies</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Trading comparables</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Fundamentals from SEC filings · price and forward consensus are your inputs, shaded</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>($ in millions, except per share)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Comparable companies</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="D6" s="5" t="inlineStr">
+    <row r="8">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>MRVL</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Src</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="9" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Share price (input)</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="9" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D11" s="17" t="n">
         <v>24514000000</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E11" s="17" t="n">
         <v>1636000000</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F11" s="17" t="n">
         <v>4853000000</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G11" s="17" t="n">
         <v>869700000</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H11" s="17" t="n">
         <v>4530000000</v>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>[1][2][3][4][5]</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="13" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="D10" s="14">
-        <f>IFERROR(D8*D9,"")</f>
-        <v/>
-      </c>
-      <c r="E10" s="14">
-        <f>IFERROR(E8*E9,"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="14">
-        <f>IFERROR(F8*F9,"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="14">
-        <f>IFERROR(G8*G9,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="14">
-        <f>IFERROR(H8*H9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="D12" s="20">
+        <f>IFERROR(D10*D11,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="20">
+        <f>IFERROR(E10*E11,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="20">
+        <f>IFERROR(F10*F11,"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="20">
+        <f>IFERROR(G10*G11,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="20">
+        <f>IFERROR(H10*H11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Capital structure (as filed)</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="9" t="inlineStr">
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Total debt</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D15" s="21" t="n">
         <v>9467000000</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E15" s="21" t="n">
         <v>4124000000</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F15" s="21" t="n">
         <v>70272000000</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G15" s="21" t="n">
         <v>4470600000</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H15" s="21" t="n">
         <v>46585000000</v>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J15" s="18" t="inlineStr">
         <is>
           <t>[6][7][8][9][10]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Cash and equivalents</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D16" s="21" t="n">
         <v>10605000000</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E16" s="21" t="n">
         <v>5539000000</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F16" s="21" t="n">
         <v>16178000000</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G16" s="21" t="n">
         <v>2638800000</v>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H16" s="21" t="n">
         <v>14265000000</v>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>[11][12][13][14][15]</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="9" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Short-term investments</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D17" s="21" t="n">
         <v>34621000000</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E17" s="21" t="n">
         <v>5013000000</v>
       </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="n">
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="n">
         <v>23151000000</v>
       </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J17" s="18" t="inlineStr">
         <is>
           <t>[16][17][18]</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Net debt / (net cash)</t>
         </is>
       </c>
-      <c r="D16" s="14">
-        <f>IFERROR(D13-D14-D15,"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="14">
-        <f>IFERROR(E13-E14-E15,"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="14">
-        <f>IFERROR(F13-F14-F15,"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="14">
-        <f>IFERROR(G13-G14-G15,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="14">
-        <f>IFERROR(H13-H14-H15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="13" t="inlineStr">
+      <c r="D18" s="20">
+        <f>IFERROR(D15-D16-D17,"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="20">
+        <f>IFERROR(E15-E16-E17,"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="20">
+        <f>IFERROR(F15-F16-F17,"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="20">
+        <f>IFERROR(G15-G16-G17,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="20">
+        <f>IFERROR(H15-H16-H17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="D17" s="14">
-        <f>IFERROR(D10+D16,"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="14">
-        <f>IFERROR(E10+E16,"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="14">
-        <f>IFERROR(F10+F16,"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="14">
-        <f>IFERROR(G10+G16,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="14">
-        <f>IFERROR(H10+H16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="7" t="inlineStr">
+      <c r="D19" s="20">
+        <f>IFERROR(D12+D18,"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="20">
+        <f>IFERROR(E12+E18,"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="20">
+        <f>IFERROR(F12+F18,"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="20">
+        <f>IFERROR(G12+G18,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="20">
+        <f>IFERROR(H12+H18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Operating (latest fiscal year as filed)</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Fiscal year end</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="17" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Period covered</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="9" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D24" s="21" t="n">
         <v>215938000000</v>
       </c>
-      <c r="E22" s="15" t="n">
+      <c r="E24" s="21" t="n">
         <v>34639000000</v>
       </c>
-      <c r="F22" s="15" t="n">
+      <c r="F24" s="21" t="n">
         <v>63887000000</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G24" s="21" t="n">
         <v>8194600000</v>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H24" s="21" t="n">
         <v>52853000000</v>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>[19][20][21][22][23]</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="9" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D25" s="21" t="n">
         <v>153463000000</v>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="E25" s="21" t="n">
         <v>17152000000</v>
       </c>
-      <c r="F23" s="15" t="n">
+      <c r="F25" s="21" t="n">
         <v>43294000000</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G25" s="21" t="n">
         <v>4180700000</v>
       </c>
-      <c r="H23" s="15" t="n">
+      <c r="H25" s="21" t="n">
         <v>18375000000</v>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J25" s="18" t="inlineStr">
         <is>
           <t>[24][25][26][27][28]</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="17" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % gross margin</t>
         </is>
       </c>
-      <c r="D24" s="19">
-        <f>IFERROR(D23/D22,"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="19">
-        <f>IFERROR(E23/E22,"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="19">
-        <f>IFERROR(F23/F22,"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="19">
-        <f>IFERROR(G23/G22,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="19">
-        <f>IFERROR(H23/H22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="9" t="inlineStr">
+      <c r="D26" s="24">
+        <f>IFERROR(D25/D24,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>IFERROR(E25/E24,"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="24">
+        <f>IFERROR(F25/F24,"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="24">
+        <f>IFERROR(G25/G24,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="24">
+        <f>IFERROR(H25/H24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Operating income</t>
         </is>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D27" s="21" t="n">
         <v>130387000000</v>
       </c>
-      <c r="E25" s="15" t="n">
+      <c r="E27" s="21" t="n">
         <v>3694000000</v>
       </c>
-      <c r="F25" s="15" t="n">
+      <c r="F27" s="21" t="n">
         <v>25484000000</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G27" s="21" t="n">
         <v>1322900000</v>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H27" s="21" t="n">
         <v>-2214000000</v>
       </c>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="J27" s="18" t="inlineStr">
         <is>
           <t>[29][30][31][32][33]</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D28" s="21" t="n">
         <v>2400000000</v>
       </c>
-      <c r="E26" s="15" t="n">
+      <c r="E28" s="21" t="n">
         <v>521000000</v>
       </c>
-      <c r="F26" s="15" t="n">
+      <c r="F28" s="21" t="n">
         <v>574000000</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G28" s="21" t="n">
         <v>221700000</v>
       </c>
-      <c r="H26" s="15" t="n">
+      <c r="H28" s="21" t="n">
         <v>10757000000</v>
       </c>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="J28" s="18" t="inlineStr">
         <is>
           <t>[34][35][36][37][38]</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="13" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="D27" s="14">
-        <f>IFERROR(D25+D26,"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="14">
-        <f>IFERROR(E25+E26,"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="14">
-        <f>IFERROR(F25+F26,"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="14">
-        <f>IFERROR(G25+G26,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="14">
-        <f>IFERROR(H25+H26,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="17" t="inlineStr">
+      <c r="D29" s="20">
+        <f>IFERROR(D27+D28,"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="20">
+        <f>IFERROR(E27+E28,"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="20">
+        <f>IFERROR(F27+F28,"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="20">
+        <f>IFERROR(G27+G28,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="20">
+        <f>IFERROR(H27+H28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % EBITDA margin</t>
         </is>
       </c>
-      <c r="D28" s="19">
-        <f>IFERROR(D27/D22,"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="19">
-        <f>IFERROR(E27/E22,"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="19">
-        <f>IFERROR(F27/F22,"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="19">
-        <f>IFERROR(G27/G22,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="19">
-        <f>IFERROR(H27/H22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="9" t="inlineStr">
+      <c r="D30" s="24">
+        <f>IFERROR(D29/D24,"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
+        <f>IFERROR(E29/E24,"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="24">
+        <f>IFERROR(F29/F24,"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="24">
+        <f>IFERROR(G29/G24,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="24">
+        <f>IFERROR(H29/H24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D31" s="21" t="n">
         <v>120067000000</v>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="E31" s="21" t="n">
         <v>4335000000</v>
       </c>
-      <c r="F29" s="15" t="n">
+      <c r="F31" s="21" t="n">
         <v>23126000000</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G31" s="21" t="n">
         <v>2670100000</v>
       </c>
-      <c r="H29" s="15" t="n">
+      <c r="H31" s="21" t="n">
         <v>-267000000</v>
       </c>
-      <c r="J29" s="12" t="inlineStr">
+      <c r="J31" s="18" t="inlineStr">
         <is>
           <t>[39][40][41][42][43]</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="9" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D32" s="25" t="n">
         <v>4.9</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E32" s="25" t="n">
         <v>2.65</v>
       </c>
-      <c r="F30" s="20" t="n">
+      <c r="F32" s="25" t="n">
         <v>4.77</v>
       </c>
-      <c r="G30" s="20" t="n">
+      <c r="G32" s="25" t="n">
         <v>3.07</v>
       </c>
-      <c r="H30" s="20" t="n">
+      <c r="H32" s="25" t="n">
         <v>-0.06</v>
       </c>
-      <c r="J30" s="12" t="inlineStr">
+      <c r="J32" s="18" t="inlineStr">
         <is>
           <t>[44][45][46][47][48]</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="7" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Trailing multiples</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="9" t="inlineStr">
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>EV / Revenue</t>
         </is>
       </c>
-      <c r="D33" s="21">
-        <f>IFERROR(D17/D22,"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="21">
-        <f>IFERROR(E17/E22,"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="21">
-        <f>IFERROR(F17/F22,"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="21">
-        <f>IFERROR(G17/G22,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="21">
-        <f>IFERROR(H17/H22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="9" t="inlineStr">
+      <c r="D35" s="26">
+        <f>IFERROR(D19/D24,"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="26">
+        <f>IFERROR(E19/E24,"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="26">
+        <f>IFERROR(F19/F24,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="26">
+        <f>IFERROR(G19/G24,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="26">
+        <f>IFERROR(H19/H24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>EV / EBITDA</t>
         </is>
       </c>
-      <c r="D34" s="21">
-        <f>IFERROR(D17/D27,"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="21">
-        <f>IFERROR(E17/E27,"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="21">
-        <f>IFERROR(F17/F27,"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="21">
-        <f>IFERROR(G17/G27,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="21">
-        <f>IFERROR(H17/H27,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="9" t="inlineStr">
+      <c r="D36" s="26">
+        <f>IFERROR(D19/D29,"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="26">
+        <f>IFERROR(E19/E29,"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="26">
+        <f>IFERROR(F19/F29,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="26">
+        <f>IFERROR(G19/G29,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="26">
+        <f>IFERROR(H19/H29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>P / E</t>
         </is>
       </c>
-      <c r="D35" s="21">
-        <f>IFERROR(D8/D30,"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="21">
-        <f>IFERROR(E8/E30,"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="21">
-        <f>IFERROR(F8/F30,"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="21">
-        <f>IFERROR(G8/G30,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="21">
-        <f>IFERROR(H8/H30,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="7" t="inlineStr">
+      <c r="D37" s="26">
+        <f>IFERROR(D10/D32,"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="26">
+        <f>IFERROR(E10/E32,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="26">
+        <f>IFERROR(F10/F32,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="26">
+        <f>IFERROR(G10/G32,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="26">
+        <f>IFERROR(H10/H32,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Forward consensus (your input — not from filings)</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="9" t="inlineStr">
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>NTM revenue (input)</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="9" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>NTM EBITDA (input)</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="9" t="inlineStr">
+      <c r="D41" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>NTM EPS (input)</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="9" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>EV / NTM revenue</t>
         </is>
       </c>
-      <c r="D41" s="21">
-        <f>IFERROR(D17/D38,"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="21">
-        <f>IFERROR(E17/E38,"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="21">
-        <f>IFERROR(F17/F38,"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="21">
-        <f>IFERROR(G17/G38,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="21">
-        <f>IFERROR(H17/H38,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="9" t="inlineStr">
+      <c r="D43" s="26">
+        <f>IFERROR(D19/D40,"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="26">
+        <f>IFERROR(E19/E40,"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="26">
+        <f>IFERROR(F19/F40,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="26">
+        <f>IFERROR(G19/G40,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="26">
+        <f>IFERROR(H19/H40,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>EV / NTM EBITDA</t>
         </is>
       </c>
-      <c r="D42" s="21">
-        <f>IFERROR(D17/D39,"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="21">
-        <f>IFERROR(E17/E39,"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="21">
-        <f>IFERROR(F17/F39,"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="21">
-        <f>IFERROR(G17/G39,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="21">
-        <f>IFERROR(H17/H39,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="9" t="inlineStr">
+      <c r="D44" s="26">
+        <f>IFERROR(D19/D41,"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="26">
+        <f>IFERROR(E19/E41,"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="26">
+        <f>IFERROR(F19/F41,"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="26">
+        <f>IFERROR(G19/G41,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="26">
+        <f>IFERROR(H19/H41,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>Forward P / E</t>
         </is>
       </c>
-      <c r="D43" s="21">
-        <f>IFERROR(D8/D40,"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="21">
-        <f>IFERROR(E8/E40,"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="21">
-        <f>IFERROR(F8/F40,"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="21">
-        <f>IFERROR(G8/G40,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="21">
-        <f>IFERROR(H8/H40,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="7" t="inlineStr">
+      <c r="D45" s="26">
+        <f>IFERROR(D10/D42,"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="26">
+        <f>IFERROR(E10/E42,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="26">
+        <f>IFERROR(F10/F42,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="26">
+        <f>IFERROR(G10/G42,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="26">
+        <f>IFERROR(H10/H42,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Set statistics</t>
         </is>
       </c>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="17" t="inlineStr">
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Trailing EV / Revenue — median</t>
         </is>
       </c>
-      <c r="D46" s="23">
-        <f>IFERROR(MEDIAN(D33:H33),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="17" t="inlineStr">
+      <c r="D48" s="28">
+        <f>IFERROR(MEDIAN(D35:H35),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Trailing EV / Revenue — mean</t>
         </is>
       </c>
-      <c r="D47" s="23">
-        <f>IFERROR(AVERAGE(D33:H33),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="17" t="inlineStr">
+      <c r="D49" s="28">
+        <f>IFERROR(AVERAGE(D35:H35),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Trailing EV / EBITDA — median</t>
         </is>
       </c>
-      <c r="D48" s="23">
-        <f>IFERROR(MEDIAN(D34:H34),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="17" t="inlineStr">
+      <c r="D50" s="28">
+        <f>IFERROR(MEDIAN(D36:H36),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Trailing EV / EBITDA — mean</t>
         </is>
       </c>
-      <c r="D49" s="23">
-        <f>IFERROR(AVERAGE(D34:H34),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="17" t="inlineStr">
+      <c r="D51" s="28">
+        <f>IFERROR(AVERAGE(D36:H36),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Trailing P / E — median</t>
         </is>
       </c>
-      <c r="D50" s="23">
-        <f>IFERROR(MEDIAN(D35:H35),"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="17" t="inlineStr">
+      <c r="D52" s="28">
+        <f>IFERROR(MEDIAN(D37:H37),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Trailing P / E — mean</t>
         </is>
       </c>
-      <c r="D51" s="23">
-        <f>IFERROR(AVERAGE(D35:H35),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="17" t="inlineStr">
+      <c r="D53" s="28">
+        <f>IFERROR(AVERAGE(D37:H37),"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Forward EV / Revenue — median</t>
         </is>
       </c>
-      <c r="D52" s="23">
-        <f>IFERROR(MEDIAN(D41:H41),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="17" t="inlineStr">
+      <c r="D54" s="28">
+        <f>IFERROR(MEDIAN(D43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Forward EV / Revenue — mean</t>
         </is>
       </c>
-      <c r="D53" s="23">
-        <f>IFERROR(AVERAGE(D41:H41),"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="17" t="inlineStr">
+      <c r="D55" s="28">
+        <f>IFERROR(AVERAGE(D43:H43),"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Forward EV / EBITDA — median</t>
         </is>
       </c>
-      <c r="D54" s="23">
-        <f>IFERROR(MEDIAN(D42:H42),"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="17" t="inlineStr">
+      <c r="D56" s="28">
+        <f>IFERROR(MEDIAN(D44:H44),"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Forward EV / EBITDA — mean</t>
         </is>
       </c>
-      <c r="D55" s="23">
-        <f>IFERROR(AVERAGE(D42:H42),"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="17" t="inlineStr">
+      <c r="D57" s="28">
+        <f>IFERROR(AVERAGE(D44:H44),"")</f>
+        <v/>
+      </c>
+      <c r="E57" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Forward P / E — median</t>
         </is>
       </c>
-      <c r="D56" s="23">
-        <f>IFERROR(MEDIAN(D43:H43),"")</f>
-        <v/>
-      </c>
-      <c r="E56" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="17" t="inlineStr">
+      <c r="D58" s="28">
+        <f>IFERROR(MEDIAN(D45:H45),"")</f>
+        <v/>
+      </c>
+      <c r="E58" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Forward P / E — mean</t>
         </is>
       </c>
-      <c r="D57" s="23">
-        <f>IFERROR(AVERAGE(D43:H43),"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="25" t="inlineStr">
+      <c r="D59" s="28">
+        <f>IFERROR(AVERAGE(D45:H45),"")</f>
+        <v/>
+      </c>
+      <c r="E59" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="30" t="inlineStr">
         <is>
           <t>Shaded blue cells are yours to fill: price and consensus are not filing data, so this workbook will not guess them.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="25" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>Multiples recompute from the cells above. Never hard-code a multiple.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="25" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="30" t="inlineStr">
         <is>
           <t>CALENDARISATION REQUIRED: these filers do not share a fiscal year end (Dec, Jan, Nov). The multiples above compare different twelve-month windows. Calendarise to a common year end before using them, and say in the footnote which filers were adjusted and how.</t>
         </is>
@@ -1890,16 +2369,25 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K808080L3VLUP&amp;R&amp;8 &amp;K808080Page &amp;P of &amp;N — see Cover for notices</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D38"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1909,311 +2397,335 @@
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>NVDA comparable companies</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Inclusion and rejection rationale</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Why each name is in the set</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="25" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Fill the rationale column before you show this to anyone. Business-model similarity, size band, growth band, margin structure and end-market exposure are the five tests that survive scrutiny.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="9" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>NVDA — NVIDIA CORP</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="9" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>AMD — ADVANCED MICRO DEVICES INC</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="9" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>AVGO — Broadcom Inc.</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="9" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>MRVL — Marvell Technology, Inc.</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>INTC — INTEL CORP</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>[rationale: business model / size / growth / margins / end market]</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Names considered and rejected</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="25" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>An empty rejection list is a red flag. If you did not reject anyone, you did not build a set, you took a sector list.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="9" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="9" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D22" s="31" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="9" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D23" s="31" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="9" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D24" s="31" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="9" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>[rejected ticker]</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>[reason for rejection]</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="7" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Calendarisation</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D28" s="31" t="inlineStr">
         <is>
           <t>Fiscal year ends Jan · latest period FY2026</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>Fiscal year ends Dec · latest period FY2025</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D30" s="31" t="inlineStr">
         <is>
           <t>Fiscal year ends Nov · latest period FY2025</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="9" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>MRVL</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>Fiscal year ends Jan · latest period FY2026</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="9" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D32" s="31" t="inlineStr">
         <is>
           <t>Fiscal year ends Dec · latest period FY2025</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="25" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>Year ends differ across the set. State the common year end you calendarised to and which filers were stubbed, or the comparison is not a comparison.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Adjustments made</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="25" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Note every adjustment here: stock-based compensation treatment, operating leases capitalised or not, non-recurring items excluded, fiscal-year calendarisation. An unstated adjustment is the fastest way to lose the room.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="9" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>[adjustment]</t>
         </is>
       </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>[what and why]</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="9" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>[adjustment]</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D38" s="31" t="inlineStr">
         <is>
           <t>[what and why]</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="9" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>[adjustment]</t>
         </is>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D39" s="31" t="inlineStr">
         <is>
           <t>[what and why]</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="9" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>[adjustment]</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D40" s="31" t="inlineStr">
         <is>
           <t>[what and why]</t>
         </is>
@@ -2222,16 +2734,25 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K808080L3VLUP&amp;R&amp;8 &amp;K808080Page &amp;P of &amp;N — see Cover for notices</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2242,1256 +2763,1280 @@
     <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>NVDA comparable companies</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Sources and audit trail</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Every marker in the [n] column of any tab resolves here. Historic financials come from filings, never from an aggregator.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="27" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Share price and forward consensus are user inputs and carry no filing provenance by design.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Accession</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="28" t="n">
+    <row r="9">
+      <c r="B9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2026 10-K</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2026-01-25 · shares · filed 2026-02-25</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>0001045810-26-000021</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F9" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="28" t="n">
+    <row r="10">
+      <c r="B10" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-12-27 · shares · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F9" s="29" t="inlineStr">
+      <c r="F10" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="28" t="n">
+    <row r="11">
+      <c r="B11" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-11-02 · shares · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F10" s="29" t="inlineStr">
+      <c r="F11" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="28" t="n">
+    <row r="12">
+      <c r="B12" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2026-01-31 · shares · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F11" s="29" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="28" t="n">
+    <row r="13">
+      <c r="B13" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-12-27 · shares · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F12" s="29" t="inlineStr">
+      <c r="F13" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="28" t="n">
+    <row r="14">
+      <c r="B14" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2026 10-K</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebt · period ending 2026-01-25 · USD · filed 2026-02-25</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>0001045810-26-000021</t>
         </is>
       </c>
-      <c r="F13" s="29" t="inlineStr">
+      <c r="F14" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="28" t="n">
+    <row r="15">
+      <c r="B15" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F15" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="28" t="n">
+    <row r="16">
+      <c r="B16" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F16" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="28" t="n">
+    <row r="17">
+      <c r="B17" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebtNoncurrent · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F17" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="28" t="n">
+    <row r="18">
+      <c r="B18" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebtNoncurrent · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="F18" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="28" t="n">
+    <row r="19">
+      <c r="B19" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2026 10-K</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2026-01-25 · USD · filed 2026-02-25</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>0001045810-26-000021</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F19" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="28" t="n">
+    <row r="20">
+      <c r="B20" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F19" s="29" t="inlineStr">
+      <c r="F20" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="28" t="n">
+    <row r="21">
+      <c r="B21" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F20" s="29" t="inlineStr">
+      <c r="F21" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="28" t="n">
+    <row r="22">
+      <c r="B22" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>us-gaap:CashCashEquivalentsRestrictedCashAndRestrictedCashEquivalents · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F22" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="28" t="n">
+    <row r="23">
+      <c r="B23" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
+      <c r="F23" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="28" t="n">
+    <row r="24">
+      <c r="B24" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2025 10-K</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>us-gaap:MarketableSecuritiesCurrent · period ending 2025-01-26 · USD · filed 2025-02-26</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>0001045810-25-000023</t>
         </is>
       </c>
-      <c r="F23" s="29" t="inlineStr">
+      <c r="F24" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581025000023/0001045810-25-000023-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="28" t="n">
+    <row r="25">
+      <c r="B25" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>us-gaap:ShortTermInvestments · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F25" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="28" t="n">
+    <row r="26">
+      <c r="B26" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>us-gaap:AvailableForSaleSecuritiesDebtSecuritiesCurrent · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F25" s="29" t="inlineStr">
+      <c r="F26" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="28" t="n">
+    <row r="27">
+      <c r="B27" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2026 10-K</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>us-gaap:Revenues · period ending 2026-01-25 · USD · filed 2026-02-25</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>0001045810-26-000021</t>
         </is>
       </c>
-      <c r="F26" s="29" t="inlineStr">
+      <c r="F27" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="28" t="n">
+    <row r="28">
+      <c r="B28" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F27" s="29" t="inlineStr">
+      <c r="F28" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="28" t="n">
+    <row r="29">
+      <c r="B29" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F28" s="29" t="inlineStr">
+      <c r="F29" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="28" t="n">
+    <row r="30">
+      <c r="B30" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F29" s="29" t="inlineStr">
+      <c r="F30" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="28" t="n">
+    <row r="31">
+      <c r="B31" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F30" s="29" t="inlineStr">
+      <c r="F31" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="28" t="n">
+    <row r="32">
+      <c r="B32" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2026 10-K</t>
         </is>
       </c>
-      <c r="D31" s="28" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2026-01-25 · USD · filed 2026-02-25</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>0001045810-26-000021</t>
         </is>
       </c>
-      <c r="F31" s="29" t="inlineStr">
+      <c r="F32" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="28" t="n">
+    <row r="33">
+      <c r="B33" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D32" s="28" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F32" s="29" t="inlineStr">
+      <c r="F33" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="28" t="n">
+    <row r="34">
+      <c r="B34" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D33" s="28" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E34" s="33" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F33" s="29" t="inlineStr">
+      <c r="F34" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="28" t="n">
+    <row r="35">
+      <c r="B35" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E35" s="33" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F34" s="29" t="inlineStr">
+      <c r="F35" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="28" t="n">
+    <row r="36">
+      <c r="B36" s="33" t="n">
         <v>28</v>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F35" s="29" t="inlineStr">
+      <c r="F36" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="28" t="n">
+    <row r="37">
+      <c r="B37" s="33" t="n">
         <v>29</v>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2026 10-K</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2026-01-25 · USD · filed 2026-02-25</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E37" s="33" t="inlineStr">
         <is>
           <t>0001045810-26-000021</t>
         </is>
       </c>
-      <c r="F36" s="29" t="inlineStr">
+      <c r="F37" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="28" t="n">
+    <row r="38">
+      <c r="B38" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D37" s="28" t="inlineStr">
+      <c r="D38" s="33" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E38" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F37" s="29" t="inlineStr">
+      <c r="F38" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="28" t="n">
+    <row r="39">
+      <c r="B39" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D38" s="28" t="inlineStr">
+      <c r="D39" s="33" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="E39" s="33" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F38" s="29" t="inlineStr">
+      <c r="F39" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="28" t="n">
+    <row r="40">
+      <c r="B40" s="33" t="n">
         <v>32</v>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D39" s="28" t="inlineStr">
+      <c r="D40" s="33" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E39" s="28" t="inlineStr">
+      <c r="E40" s="33" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F39" s="29" t="inlineStr">
+      <c r="F40" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="28" t="n">
+    <row r="41">
+      <c r="B41" s="33" t="n">
         <v>33</v>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D40" s="28" t="inlineStr">
+      <c r="D41" s="33" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E40" s="28" t="inlineStr">
+      <c r="E41" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F40" s="29" t="inlineStr">
+      <c r="F41" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="28" t="n">
+    <row r="42">
+      <c r="B42" s="33" t="n">
         <v>34</v>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2026 10-K</t>
         </is>
       </c>
-      <c r="D41" s="28" t="inlineStr">
+      <c r="D42" s="33" t="inlineStr">
         <is>
           <t>us-gaap:Depreciation · period ending 2026-01-25 · USD · filed 2026-02-25</t>
         </is>
       </c>
-      <c r="E41" s="28" t="inlineStr">
+      <c r="E42" s="33" t="inlineStr">
         <is>
           <t>0001045810-26-000021</t>
         </is>
       </c>
-      <c r="F41" s="29" t="inlineStr">
+      <c r="F42" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="28" t="n">
+    <row r="43">
+      <c r="B43" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D42" s="28" t="inlineStr">
+      <c r="D43" s="33" t="inlineStr">
         <is>
           <t>us-gaap:Depreciation · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E42" s="28" t="inlineStr">
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F42" s="29" t="inlineStr">
+      <c r="F43" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="28" t="n">
+    <row r="44">
+      <c r="B44" s="33" t="n">
         <v>36</v>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D43" s="28" t="inlineStr">
+      <c r="D44" s="33" t="inlineStr">
         <is>
           <t>us-gaap:Depreciation · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E43" s="28" t="inlineStr">
+      <c r="E44" s="33" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F43" s="29" t="inlineStr">
+      <c r="F44" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="28" t="n">
+    <row r="45">
+      <c r="B45" s="33" t="n">
         <v>37</v>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D44" s="28" t="inlineStr">
+      <c r="D45" s="33" t="inlineStr">
         <is>
           <t>us-gaap:Depreciation · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E44" s="28" t="inlineStr">
+      <c r="E45" s="33" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F44" s="29" t="inlineStr">
+      <c r="F45" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="28" t="n">
+    <row r="46">
+      <c r="B46" s="33" t="n">
         <v>38</v>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D45" s="28" t="inlineStr">
+      <c r="D46" s="33" t="inlineStr">
         <is>
           <t>us-gaap:Depreciation · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E45" s="28" t="inlineStr">
+      <c r="E46" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F45" s="29" t="inlineStr">
+      <c r="F46" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="28" t="n">
+    <row r="47">
+      <c r="B47" s="33" t="n">
         <v>39</v>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2026 10-K</t>
         </is>
       </c>
-      <c r="D46" s="28" t="inlineStr">
+      <c r="D47" s="33" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2026-01-25 · USD · filed 2026-02-25</t>
         </is>
       </c>
-      <c r="E46" s="28" t="inlineStr">
+      <c r="E47" s="33" t="inlineStr">
         <is>
           <t>0001045810-26-000021</t>
         </is>
       </c>
-      <c r="F46" s="29" t="inlineStr">
+      <c r="F47" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="28" t="n">
+    <row r="48">
+      <c r="B48" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D47" s="28" t="inlineStr">
+      <c r="D48" s="33" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2025-12-27 · USD · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E47" s="28" t="inlineStr">
+      <c r="E48" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F47" s="29" t="inlineStr">
+      <c r="F48" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="28" t="n">
+    <row r="49">
+      <c r="B49" s="33" t="n">
         <v>41</v>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D48" s="28" t="inlineStr">
+      <c r="D49" s="33" t="inlineStr">
         <is>
           <t>us-gaap:ProfitLoss · period ending 2025-11-02 · USD · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E48" s="28" t="inlineStr">
+      <c r="E49" s="33" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F48" s="29" t="inlineStr">
+      <c r="F49" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="28" t="n">
+    <row r="50">
+      <c r="B50" s="33" t="n">
         <v>42</v>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D49" s="28" t="inlineStr">
+      <c r="D50" s="33" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2026-01-31 · USD · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E49" s="28" t="inlineStr">
+      <c r="E50" s="33" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F49" s="29" t="inlineStr">
+      <c r="F50" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="28" t="n">
+    <row r="51">
+      <c r="B51" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C51" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D50" s="28" t="inlineStr">
+      <c r="D51" s="33" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2025-12-27 · USD · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E50" s="28" t="inlineStr">
+      <c r="E51" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F50" s="29" t="inlineStr">
+      <c r="F51" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="28" t="n">
+    <row r="52">
+      <c r="B52" s="33" t="n">
         <v>44</v>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>NVDA FY2026 10-K</t>
         </is>
       </c>
-      <c r="D51" s="28" t="inlineStr">
+      <c r="D52" s="33" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2026-01-25 · USD/shares · filed 2026-02-25</t>
         </is>
       </c>
-      <c r="E51" s="28" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>0001045810-26-000021</t>
         </is>
       </c>
-      <c r="F51" s="29" t="inlineStr">
+      <c r="F52" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1045810/000104581026000021/0001045810-26-000021-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="28" t="n">
+    <row r="53">
+      <c r="B53" s="33" t="n">
         <v>45</v>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>AMD FY2025 10-K</t>
         </is>
       </c>
-      <c r="D52" s="28" t="inlineStr">
+      <c r="D53" s="33" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2025-12-27 · USD/shares · filed 2026-02-04</t>
         </is>
       </c>
-      <c r="E52" s="28" t="inlineStr">
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>0000002488-26-000018</t>
         </is>
       </c>
-      <c r="F52" s="29" t="inlineStr">
+      <c r="F53" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/2488/000000248826000018/0000002488-26-000018-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="28" t="n">
+    <row r="54">
+      <c r="B54" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>AVGO FY2025 10-K</t>
         </is>
       </c>
-      <c r="D53" s="28" t="inlineStr">
+      <c r="D54" s="33" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2025-11-02 · USD/shares · filed 2025-12-18</t>
         </is>
       </c>
-      <c r="E53" s="28" t="inlineStr">
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>0001730168-25-000121</t>
         </is>
       </c>
-      <c r="F53" s="29" t="inlineStr">
+      <c r="F54" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1730168/000173016825000121/0001730168-25-000121-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="28" t="n">
+    <row r="55">
+      <c r="B55" s="33" t="n">
         <v>47</v>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
         <is>
           <t>MRVL FY2026 10-K</t>
         </is>
       </c>
-      <c r="D54" s="28" t="inlineStr">
+      <c r="D55" s="33" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2026-01-31 · USD/shares · filed 2026-03-11</t>
         </is>
       </c>
-      <c r="E54" s="28" t="inlineStr">
+      <c r="E55" s="33" t="inlineStr">
         <is>
           <t>0001835632-26-000011</t>
         </is>
       </c>
-      <c r="F54" s="29" t="inlineStr">
+      <c r="F55" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1835632/000183563226000011/0001835632-26-000011-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="28" t="n">
+    <row r="56">
+      <c r="B56" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C56" s="15" t="inlineStr">
         <is>
           <t>INTC FY2025 10-K</t>
         </is>
       </c>
-      <c r="D55" s="28" t="inlineStr">
+      <c r="D56" s="33" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2025-12-27 · USD/shares · filed 2026-01-23</t>
         </is>
       </c>
-      <c r="E55" s="28" t="inlineStr">
+      <c r="E56" s="33" t="inlineStr">
         <is>
           <t>0000050863-26-000011</t>
         </is>
       </c>
-      <c r="F55" s="29" t="inlineStr">
+      <c r="F56" s="34" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/50863/000005086326000011/0000050863-26-000011-index.htm</t>
         </is>
@@ -3499,55 +4044,56 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId49"/>
 </worksheet>
 </file>
--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 24 August 2026 at 11:21 UTC</t>
+          <t>Generated 24 August 2026 at 19:54 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 24 August 2026 at 19:54 UTC</t>
+          <t>Generated 25 August 2026 at 08:57 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 August 2026 at 08:57 UTC</t>
+          <t>Generated 25 August 2026 at 09:00 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 August 2026 at 09:00 UTC</t>
+          <t>Generated 25 August 2026 at 09:17 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 August 2026 at 09:17 UTC</t>
+          <t>Generated 25 August 2026 at 09:19 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 August 2026 at 09:19 UTC</t>
+          <t>Generated 26 August 2026 at 07:28 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 26 August 2026 at 07:28 UTC</t>
+          <t>Generated 27 August 2026 at 17:52 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 27 August 2026 at 17:52 UTC</t>
+          <t>Generated 28 August 2026 at 09:22 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 09:22 UTC</t>
+          <t>Generated 28 August 2026 at 10:01 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 10:01 UTC</t>
+          <t>Generated 28 August 2026 at 10:29 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 10:29 UTC</t>
+          <t>Generated 28 August 2026 at 12:34 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 12:34 UTC</t>
+          <t>Generated 28 August 2026 at 12:41 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 12:41 UTC</t>
+          <t>Generated 28 August 2026 at 18:58 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 18:58 UTC</t>
+          <t>Generated 29 August 2026 at 12:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
     <row r="15">
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>MRVL — Marvell Technology, Inc.</t>
+          <t>MRVL — MARVELL TECHNOLOGY, INC</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 29 August 2026 at 12:49 UTC</t>
+          <t>Generated 29 August 2026 at 23:34 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 29 August 2026 at 23:34 UTC</t>
+          <t>Generated 30 August 2026 at 12:11 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 30 August 2026 at 12:11 UTC</t>
+          <t>Generated 31 August 2026 at 14:21 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 31 August 2026 at 14:21 UTC</t>
+          <t>Generated 01 September 2026 at 11:58 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 01 September 2026 at 11:58 UTC</t>
+          <t>Generated 02 September 2026 at 11:41 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 02 September 2026 at 11:41 UTC</t>
+          <t>Generated 03 September 2026 at 11:40 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 03 September 2026 at 11:40 UTC</t>
+          <t>Generated 04 September 2026 at 11:41 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 04 September 2026 at 11:41 UTC</t>
+          <t>Generated 05 September 2026 at 10:54 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 05 September 2026 at 10:54 UTC</t>
+          <t>Generated 06 September 2026 at 11:18 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 06 September 2026 at 11:18 UTC</t>
+          <t>Generated 07 September 2026 at 12:59 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 07 September 2026 at 12:59 UTC</t>
+          <t>Generated 08 September 2026 at 11:41 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 08 September 2026 at 11:41 UTC</t>
+          <t>Generated 09 September 2026 at 11:48 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 09 September 2026 at 11:48 UTC</t>
+          <t>Generated 10 September 2026 at 11:45 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 10 September 2026 at 11:45 UTC</t>
+          <t>Generated 11 September 2026 at 11:45 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_comps.xlsx
+++ b/samples/NVDA_comps.xlsx
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 11 September 2026 at 11:45 UTC</t>
+          <t>Generated 12 September 2026 at 11:12 UTC</t>
         </is>
       </c>
     </row>
